--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.14378592720747</v>
+        <v>7.498365213171215</v>
       </c>
       <c r="D2" t="n">
-        <v>59.3992028011053</v>
+        <v>9.652370455179611</v>
       </c>
       <c r="E2" t="n">
-        <v>10.01295824782863</v>
+        <v>1.627105715272152</v>
       </c>
       <c r="F2" t="n">
-        <v>13.5946821986792</v>
+        <v>2.20913585728537</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.49391285608831</v>
+        <v>10.96776083911435</v>
       </c>
       <c r="D3" t="n">
-        <v>23.19167084572999</v>
+        <v>3.768646512431124</v>
       </c>
       <c r="E3" t="n">
-        <v>10.01295824782863</v>
+        <v>1.627105715272152</v>
       </c>
       <c r="F3" t="n">
-        <v>13.5946821986792</v>
+        <v>2.20913585728537</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.95306917337948</v>
+        <v>6.979873740674165</v>
       </c>
       <c r="D4" t="n">
-        <v>30.57014665963894</v>
+        <v>4.967648832191327</v>
       </c>
       <c r="E4" t="n">
-        <v>10.01295824782863</v>
+        <v>1.627105715272152</v>
       </c>
       <c r="F4" t="n">
-        <v>13.5946821986792</v>
+        <v>2.20913585728537</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.45524920317231</v>
+        <v>7.2239779955155</v>
       </c>
       <c r="D5" t="n">
-        <v>34.64767529032384</v>
+        <v>5.630247234677624</v>
       </c>
       <c r="E5" t="n">
-        <v>10.01295824782863</v>
+        <v>1.627105715272152</v>
       </c>
       <c r="F5" t="n">
-        <v>13.5946821986792</v>
+        <v>2.20913585728537</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
